--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,61 +472,51 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n_cores</t>
+          <t>n_samples</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>n_samples</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>280</v>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="B7" t="b">
-        <v>1</v>
+          <t>Runtime (hours)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0384520298242569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Runtime (hours)</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06862882117430369</v>
+        <v>150.3693606337602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>Criterion Evaluations</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150.3668125727713</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Criterion Evaluations</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>8741</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0384520298242569</v>
+        <v>0.02321127315362295</v>
       </c>
     </row>
     <row r="8">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>150.3693606337602</v>
+        <v>150.3692726695184</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>629</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02321127315362295</v>
+        <v>0.02358474294344584</v>
       </c>
     </row>
     <row r="8">

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -486,37 +486,7 @@
         </is>
       </c>
       <c r="B6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Runtime (hours)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.02358474294344584</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>150.3692726695184</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Criterion Evaluations</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,37 @@
         </is>
       </c>
       <c r="B6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Runtime (hours)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0913918364710278</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>165.5407492499305</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Criterion Evaluations</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>409</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>840</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
@@ -486,37 +486,7 @@
         </is>
       </c>
       <c r="B6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Runtime (hours)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0913918364710278</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>165.5407492499305</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Criterion Evaluations</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>409</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,21 +472,61 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>n_cores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>280</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>n_samples</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>Finished</t>
         </is>
       </c>
-      <c r="B6" t="b">
-        <v>0</v>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Runtime (hours)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.01616479727956984</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>150.369411856284</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Criterion Evaluations</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01616479727956984</v>
+        <v>0.4608053288857142</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150.369411856284</v>
+        <v>261.7777274348612</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>246</v>
+        <v>5167</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>560</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4608053288857142</v>
+        <v>0.05559492925802867</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>261.7777274348612</v>
+        <v>151.284515522424</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5167</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -496,37 +496,7 @@
         </is>
       </c>
       <c r="B7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Runtime (hours)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.05559492925802867</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>151.284515522424</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Criterion Evaluations</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,37 @@
         </is>
       </c>
       <c r="B7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Runtime (hours)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.01436295588811239</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>151.2845155226983</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Criterion Evaluations</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01436295588811239</v>
+        <v>0.5001331871085697</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151.2845155226983</v>
+        <v>160.9732182624511</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>2941</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5001331871085697</v>
+        <v>0.05345776226785448</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160.9732182624511</v>
+        <v>152.9133868684542</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2941</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05345776226785448</v>
+        <v>0.05747065411673652</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152.9133868684542</v>
+        <v>152.9132209406655</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/search_model_2Type/log/Est1_estimation_options.xlsx
+++ b/search_model_2Type/log/Est1_estimation_options.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05747065411673652</v>
+        <v>0.05572963953018188</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152.9132209406655</v>
+        <v>145.351347957675</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>173</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
